--- a/TENNISSA-Initial-Budget-FY2027-FY2028.xlsx
+++ b/TENNISSA-Initial-Budget-FY2027-FY2028.xlsx
@@ -273,7 +273,7 @@
     <t xml:space="preserve">Stipend per person per month ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Owner-provided rate.</t>
+    <t xml:space="preserve">Owner-provided rate (updated Oct 29, 2026 from $250).</t>
   </si>
   <si>
     <t xml:space="preserve">Months paid in the year</t>
@@ -492,7 +492,7 @@
     <t xml:space="preserve">   Operational staff stipends</t>
   </si>
   <si>
-    <t xml:space="preserve">Requested line. Staff count × $250/month × months (Assumptions tab).</t>
+    <t xml:space="preserve">Requested line. Staff count × monthly stipend × months (Assumptions tab).</t>
   </si>
   <si>
     <t xml:space="preserve">   Executive Director compensation</t>
@@ -1496,15 +1496,15 @@
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">Budget!B77</f>
-        <v>51450</v>
+        <v>57750</v>
       </c>
       <c r="C12" s="6" t="n">
         <f aca="false">Budget!C77</f>
-        <v>60411.75</v>
+        <v>69861.75</v>
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">B12+C12</f>
-        <v>111861.75</v>
+        <v>127611.75</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1513,15 +1513,15 @@
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">Budget!B80</f>
-        <v>-9482</v>
+        <v>-15782</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Budget!C80</f>
-        <v>5115.962</v>
+        <v>-4334.038</v>
       </c>
       <c r="D13" s="7" t="n">
         <f aca="false">B13+C13</f>
-        <v>-4366.038</v>
+        <v>-20116.038</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1530,11 +1530,11 @@
       </c>
       <c r="B14" s="6" t="n">
         <f aca="false">Budget!B82</f>
-        <v>-9482</v>
+        <v>-15782</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">Budget!C82</f>
-        <v>-4366.038</v>
+        <v>-20116.038</v>
       </c>
       <c r="D14" s="2"/>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E5" s="13" t="n">
         <f aca="false">IFERROR(C5/C$14,0)</f>
-        <v>0.273125675054936</v>
+        <v>0.236180742681081</v>
       </c>
       <c r="F5" s="17" t="n">
         <f aca="false">C5/12</f>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E6" s="13" t="n">
         <f aca="false">IFERROR(C6/C$14,0)</f>
-        <v>0.27089101044085</v>
+        <v>0.234248354786417</v>
       </c>
       <c r="F6" s="17" t="n">
         <f aca="false">C6/12</f>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E7" s="13" t="n">
         <f aca="false">IFERROR(C7/C$14,0)</f>
-        <v>0.114216191386609</v>
+        <v>0.0987664923939065</v>
       </c>
       <c r="F7" s="17" t="n">
         <f aca="false">C7/12</f>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="E8" s="13" t="n">
         <f aca="false">IFERROR(C8/C$14,0)</f>
-        <v>0.0331061424309013</v>
+        <v>0.028627968809828</v>
       </c>
       <c r="F8" s="17" t="n">
         <f aca="false">C8/12</f>
@@ -1847,23 +1847,23 @@
       </c>
       <c r="B9" s="6" t="n">
         <f aca="false">Budget!B56</f>
-        <v>6150</v>
+        <v>12150</v>
       </c>
       <c r="C9" s="6" t="n">
         <f aca="false">Budget!C56</f>
-        <v>9100</v>
+        <v>18100</v>
       </c>
       <c r="D9" s="17" t="n">
         <f aca="false">B9+C9</f>
-        <v>15250</v>
+        <v>30250</v>
       </c>
       <c r="E9" s="13" t="n">
         <f aca="false">IFERROR(C9/C$14,0)</f>
-        <v>0.150632948060601</v>
+        <v>0.259083117728943</v>
       </c>
       <c r="F9" s="17" t="n">
         <f aca="false">C9/12</f>
-        <v>758.333333333333</v>
+        <v>1508.33333333333</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="E10" s="13" t="n">
         <f aca="false">IFERROR(C10/C$14,0)</f>
-        <v>0.0695228991048927</v>
+        <v>0.0601187345006388</v>
       </c>
       <c r="F10" s="17" t="n">
         <f aca="false">C10/12</f>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E11" s="13" t="n">
         <f aca="false">IFERROR(C11/C$14,0)</f>
-        <v>0.00546251350109871</v>
+        <v>0.00472361485362162</v>
       </c>
       <c r="F11" s="17" t="n">
         <f aca="false">C11/12</f>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E12" s="13" t="n">
         <f aca="false">IFERROR(C12/C$14,0)</f>
-        <v>0.0354235724010644</v>
+        <v>0.0306319266265159</v>
       </c>
       <c r="F12" s="17" t="n">
         <f aca="false">C12/12</f>
@@ -1947,15 +1947,15 @@
       </c>
       <c r="B13" s="6" t="n">
         <f aca="false">Budget!B76</f>
-        <v>2450</v>
+        <v>2750</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Budget!C76</f>
-        <v>2876.75</v>
+        <v>3326.75</v>
       </c>
       <c r="D13" s="17" t="n">
         <f aca="false">B13+C13</f>
-        <v>5326.75</v>
+        <v>6076.75</v>
       </c>
       <c r="E13" s="13" t="n">
         <f aca="false">IFERROR(C13/C$14,0)</f>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="F13" s="17" t="n">
         <f aca="false">C13/12</f>
-        <v>239.729166666667</v>
+        <v>277.229166666667</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1972,15 +1972,15 @@
       </c>
       <c r="B14" s="19" t="n">
         <f aca="false">SUM(B5:B13)</f>
-        <v>51450</v>
+        <v>57750</v>
       </c>
       <c r="C14" s="19" t="n">
         <f aca="false">SUM(C5:C13)</f>
-        <v>60411.75</v>
+        <v>69861.75</v>
       </c>
       <c r="D14" s="19" t="n">
         <f aca="false">SUM(D5:D13)</f>
-        <v>111861.75</v>
+        <v>127611.75</v>
       </c>
       <c r="E14" s="13" t="n">
         <f aca="false">IFERROR(C14/C$14,0)</f>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F14" s="17" t="n">
         <f aca="false">C14/12</f>
-        <v>5034.3125</v>
+        <v>5821.8125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2110,15 +2110,15 @@
       </c>
       <c r="B22" s="19" t="n">
         <f aca="false">Budget!B80</f>
-        <v>-9482</v>
+        <v>-15782</v>
       </c>
       <c r="C22" s="19" t="n">
         <f aca="false">Budget!C80</f>
-        <v>5115.962</v>
+        <v>-4334.038</v>
       </c>
       <c r="D22" s="19" t="n">
         <f aca="false">B22+C22</f>
-        <v>-4366.038</v>
+        <v>-20116.038</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
@@ -2390,10 +2390,10 @@
         <v>81</v>
       </c>
       <c r="B22" s="24" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="C22" s="24" t="n">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="D22" s="23" t="s">
         <v>82</v>
@@ -3305,15 +3305,15 @@
       </c>
       <c r="B53" s="7" t="n">
         <f aca="false">Assumptions!$B$21*Assumptions!$B$22*Assumptions!$B$23</f>
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="C53" s="7" t="n">
         <f aca="false">Assumptions!$C$21*Assumptions!$C$22*Assumptions!$C$23</f>
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="D53" s="7" t="n">
         <f aca="false">B53+C53</f>
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="E53" s="23" t="s">
         <v>155</v>
@@ -3361,15 +3361,15 @@
       </c>
       <c r="B56" s="29" t="n">
         <f aca="false">SUM(B53:B55)</f>
-        <v>6150</v>
+        <v>12150</v>
       </c>
       <c r="C56" s="29" t="n">
         <f aca="false">SUM(C53:C55)</f>
-        <v>9100</v>
+        <v>18100</v>
       </c>
       <c r="D56" s="29" t="n">
         <f aca="false">SUM(D53:D55)</f>
-        <v>15250</v>
+        <v>30250</v>
       </c>
       <c r="E56" s="2"/>
     </row>
@@ -3676,15 +3676,15 @@
       </c>
       <c r="B75" s="29" t="n">
         <f aca="false">B32+B42+B48+B51+B56+B62+B69+B74</f>
-        <v>49000</v>
+        <v>55000</v>
       </c>
       <c r="C75" s="29" t="n">
         <f aca="false">C32+C42+C48+C51+C56+C62+C69+C74</f>
-        <v>57535</v>
+        <v>66535</v>
       </c>
       <c r="D75" s="29" t="n">
         <f aca="false">B75+C75</f>
-        <v>106535</v>
+        <v>121535</v>
       </c>
       <c r="E75" s="2"/>
     </row>
@@ -3694,15 +3694,15 @@
       </c>
       <c r="B76" s="7" t="n">
         <f aca="false">Assumptions!$B$26*B75</f>
-        <v>2450</v>
+        <v>2750</v>
       </c>
       <c r="C76" s="7" t="n">
         <f aca="false">Assumptions!$C$26*C75</f>
-        <v>2876.75</v>
+        <v>3326.75</v>
       </c>
       <c r="D76" s="7" t="n">
         <f aca="false">B76+C76</f>
-        <v>5326.75</v>
+        <v>6076.75</v>
       </c>
       <c r="E76" s="2"/>
     </row>
@@ -3712,15 +3712,15 @@
       </c>
       <c r="B77" s="19" t="n">
         <f aca="false">B75+B76</f>
-        <v>51450</v>
+        <v>57750</v>
       </c>
       <c r="C77" s="19" t="n">
         <f aca="false">C75+C76</f>
-        <v>60411.75</v>
+        <v>69861.75</v>
       </c>
       <c r="D77" s="19" t="n">
         <f aca="false">B77+C77</f>
-        <v>111861.75</v>
+        <v>127611.75</v>
       </c>
       <c r="E77" s="2"/>
     </row>
@@ -3746,15 +3746,15 @@
       </c>
       <c r="B80" s="20" t="n">
         <f aca="false">B24-B77</f>
-        <v>-9482</v>
+        <v>-15782</v>
       </c>
       <c r="C80" s="20" t="n">
         <f aca="false">C24-C77</f>
-        <v>5115.962</v>
+        <v>-4334.038</v>
       </c>
       <c r="D80" s="20" t="n">
         <f aca="false">B80+C80</f>
-        <v>-4366.038</v>
+        <v>-20116.038</v>
       </c>
       <c r="E80" s="2"/>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C81" s="6" t="n">
         <f aca="false">B82</f>
-        <v>-9482</v>
+        <v>-15782</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="2"/>
@@ -3779,11 +3779,11 @@
       </c>
       <c r="B82" s="19" t="n">
         <f aca="false">B81+B80</f>
-        <v>-9482</v>
+        <v>-15782</v>
       </c>
       <c r="C82" s="19" t="n">
         <f aca="false">C81+C80</f>
-        <v>-4366.038</v>
+        <v>-20116.038</v>
       </c>
       <c r="D82" s="19"/>
       <c r="E82" s="23" t="s">
@@ -3796,11 +3796,11 @@
       </c>
       <c r="B83" s="33" t="n">
         <f aca="false">IFERROR(B82/(B77/12),0)</f>
-        <v>-2.21154518950437</v>
+        <v>-3.27937662337662</v>
       </c>
       <c r="C83" s="33" t="n">
         <f aca="false">IFERROR(C82/(C77/12),0)</f>
-        <v>-0.867256055320364</v>
+        <v>-3.45528785064789</v>
       </c>
       <c r="D83" s="33"/>
       <c r="E83" s="2"/>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="B84" s="34" t="n">
         <f aca="false">IFERROR(B77/B7,0)</f>
-        <v>0.30625</v>
+        <v>0.34375</v>
       </c>
       <c r="C84" s="34" t="n">
         <f aca="false">IFERROR(C77/C7,0)</f>
-        <v>0.161098</v>
+        <v>0.186298</v>
       </c>
       <c r="D84" s="34"/>
       <c r="E84" s="23" t="s">
@@ -4100,27 +4100,27 @@
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">(Budget!B75-Budget!B36+Assumptions!$B$10*B7)*(1+Assumptions!$B$26)</f>
-        <v>48930</v>
+        <v>55230</v>
       </c>
       <c r="C12" s="7" t="n">
         <f aca="false">(Budget!C75-Budget!C36+Assumptions!$C$10*C7)*(1+Assumptions!$C$26)</f>
-        <v>54663</v>
+        <v>64113</v>
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">(Budget!B75-Budget!B36+Assumptions!$B$10*D7)*(1+Assumptions!$B$26)</f>
-        <v>51450</v>
+        <v>57750</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">(Budget!C75-Budget!C36+Assumptions!$C$10*E7)*(1+Assumptions!$C$26)</f>
-        <v>60411.75</v>
+        <v>69861.75</v>
       </c>
       <c r="F12" s="7" t="n">
         <f aca="false">(Budget!B75-Budget!B36+Assumptions!$B$10*F7)*(1+Assumptions!$B$26)</f>
-        <v>54915</v>
+        <v>61215</v>
       </c>
       <c r="G12" s="7" t="n">
         <f aca="false">(Budget!C75-Budget!C36+Assumptions!$C$10*G7)*(1+Assumptions!$C$26)</f>
-        <v>67368</v>
+        <v>76818</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,27 +4129,27 @@
       </c>
       <c r="B13" s="19" t="n">
         <f aca="false">B11-B12</f>
-        <v>-16730</v>
+        <v>-23030</v>
       </c>
       <c r="C13" s="19" t="n">
         <f aca="false">C11-C12</f>
-        <v>-11563</v>
+        <v>-21013</v>
       </c>
       <c r="D13" s="19" t="n">
         <f aca="false">D11-D12</f>
-        <v>-9650</v>
+        <v>-15950</v>
       </c>
       <c r="E13" s="19" t="n">
         <f aca="false">E11-E12</f>
-        <v>4588.25</v>
+        <v>-4861.75</v>
       </c>
       <c r="F13" s="19" t="n">
         <f aca="false">F11-F12</f>
-        <v>85</v>
+        <v>-6215</v>
       </c>
       <c r="G13" s="19" t="n">
         <f aca="false">G11-G12</f>
-        <v>24132</v>
+        <v>14682</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
